--- a/artfynd/A 17540-2025 artfynd.xlsx
+++ b/artfynd/A 17540-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122940054</v>
+        <v>122939523</v>
       </c>
       <c r="B2" t="n">
-        <v>56386</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
